--- a/Matching process/unmatched_mentees.xlsx
+++ b/Matching process/unmatched_mentees.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\LN2PEPF0000C098\EXCELCNV\6e5d4888-81e1-4fe5-8925-24ba2d8e460d\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/Matching Algorithm/Matching process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{15121F92-3C29-47CE-A67D-7325CE7C80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94DBC0C7-62CB-41F6-90A6-E25255B95A97}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{15121F92-3C29-47CE-A67D-7325CE7C80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AA5947E-1ABB-4EE7-A5C7-9398AE01FE76}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{109B5664-926B-4F5F-B371-194BCABAD1A3}"/>
+    <workbookView xWindow="25080" yWindow="2616" windowWidth="21600" windowHeight="11832" xr2:uid="{109B5664-926B-4F5F-B371-194BCABAD1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$B$1:$C$24</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
   <si>
     <t>Mentee_Email</t>
   </si>
@@ -113,16 +116,16 @@
     <t>hassmali0789@gmail.com</t>
   </si>
   <si>
-    <t>physcsi</t>
-  </si>
-  <si>
     <t>ameeraquraishi25@gmail.com</t>
   </si>
   <si>
     <t>Civil Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">des eng </t>
+    <t xml:space="preserve">done </t>
+  </si>
+  <si>
+    <t>civil</t>
   </si>
   <si>
     <t>zakirah.hassen@gmail.com</t>
@@ -150,9 +153,6 @@
   </si>
   <si>
     <t>taalayuk@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">done </t>
   </si>
   <si>
     <t>medali.talhi@gmail.com</t>
@@ -192,7 +192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,7 +328,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,6 +506,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -669,8 +675,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -730,9 +738,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -770,7 +778,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -876,7 +884,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1018,7 +1026,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1026,15 +1034,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF352312-7580-40DA-A087-87919BFEAB92}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.7109375" customWidth="1"/>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1058,8 +1067,11 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1072,11 +1084,8 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1086,8 +1095,11 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1097,11 +1109,12 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
+      <c r="D5" s="1"/>
       <c r="E5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1111,11 +1124,12 @@
       <c r="C6" t="s">
         <v>6</v>
       </c>
+      <c r="D6" s="1"/>
       <c r="E6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1125,11 +1139,12 @@
       <c r="C7" t="s">
         <v>6</v>
       </c>
+      <c r="D7" s="1"/>
       <c r="E7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1139,8 +1154,9 @@
       <c r="C8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1157,7 +1173,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1174,7 +1190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1184,25 +1200,29 @@
       <c r="C11" t="s">
         <v>6</v>
       </c>
+      <c r="D11" s="2"/>
       <c r="E11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
       </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1213,7 +1233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1230,7 +1250,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1241,7 +1261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1252,7 +1272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1263,7 +1283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1280,7 +1300,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1291,18 +1311,18 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
@@ -1311,15 +1331,15 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -1328,15 +1348,15 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
@@ -1348,38 +1368,45 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:C24" xr:uid="{BF352312-7580-40DA-A087-87919BFEAB92}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Brother"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>